--- a/Result/profitability/1310.xlsx
+++ b/Result/profitability/1310.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3725</v>
+        <v>-0.355</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.0225</v>
+        <v>-3.1225</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.39</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2825</v>
+        <v>-0.26375</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.774999999999999</v>
+        <v>-1.83375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -901,10 +901,10 @@
         <v>-0.85</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.34625</v>
+        <v>-0.3275</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.62875</v>
+        <v>-1.45</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1020,10 +1020,10 @@
         <v>-1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4725</v>
+        <v>-0.45125</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.4025</v>
+        <v>-3.4675</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>0.59</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3537500000000001</v>
+        <v>-0.3475</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8412499999999998</v>
+        <v>-0.9162499999999996</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1268,10 +1268,10 @@
         <v>0.85</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2175</v>
+        <v>-0.1875000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>1.8175</v>
+        <v>2.00375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1395,10 +1395,10 @@
         <v>0.13</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1475</v>
+        <v>-0.05375000000000003</v>
       </c>
       <c r="N8" t="n">
-        <v>3.34875</v>
+        <v>1.49625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1649,7 +1649,7 @@
         <v>-0.05</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.08500000000000005</v>
+        <v>-0.08500000000000003</v>
       </c>
       <c r="N10" t="n">
         <v>2.358750000000001</v>
@@ -1903,7 +1903,7 @@
         <v>0.01</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.01250000000000005</v>
+        <v>-0.01250000000000004</v>
       </c>
       <c r="N12" t="n">
         <v>2.21625</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2094</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-116</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-163</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-8.23%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>76</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-87</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-103</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.39625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-4.09375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7978723404255319</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-14.82</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-1.657718120805369</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4722222222222222</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.5199999999999996</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.09701492537313428</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
